--- a/Frame_NGS,embedding (260907).xlsx
+++ b/Frame_NGS,embedding (260907).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://postechackr-my.sharepoint.com/personal/sujineeda_postech_ac_kr/Documents/학회/2026/ICAE/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="8_{8FA9E7DD-83E0-4326-9857-E757EEEA8F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{134CAB7C-3C0C-4A73-ACC8-BD8DB13799C0}"/>
+  <xr:revisionPtr revIDLastSave="1214" documentId="8_{8FA9E7DD-83E0-4326-9857-E757EEEA8F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F86E29-A359-4B70-8783-626E300DB1A1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{05B644AA-31FF-4C98-95AB-980B1DBC3657}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="167">
   <si>
     <t>Introduction</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -622,12 +622,68 @@
     <t>2) Genus-tree</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relative abundance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hierarchical topology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>branch length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAC&amp;ARC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3) Genus-tree + cross-domain</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merged dataset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) Taxa-level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2) Genus-tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genus-tree + cross-domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2) ASV-tree</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>60epoch, 10 patience, early stopping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3) ASV-tree + cross-domain</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,7 +815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1040,6 +1096,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1099,6 +1168,56 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1112,7 +1231,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1243,16 +1362,13 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,11 +1377,171 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1294,15 +1570,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>107674</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>24847</xdr:rowOff>
+      <xdr:colOff>182218</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>173934</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>201543</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>62395</xdr:rowOff>
+      <xdr:colOff>276087</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>13942</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1331,7 +1607,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14428304" y="14751325"/>
+          <a:off x="14502848" y="14063869"/>
           <a:ext cx="6902174" cy="6936961"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1879,7 +2155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F457267A-5893-4DAC-B383-E26E2177278B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1888,8 +2164,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15218C2B-52AC-4F8B-B0B8-4A3A16344E12}">
-  <dimension ref="B2:AA104"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:AA164"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -1897,65 +2173,65 @@
     <col min="4" max="21" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2">
       <c r="B5" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:2">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:2">
       <c r="B14" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:2">
       <c r="B15" s="20" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:2">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12">
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
@@ -1963,7 +2239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12">
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
@@ -1971,7 +2247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1982,7 +2258,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12">
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
@@ -1993,7 +2269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12">
       <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
@@ -2022,7 +2298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12">
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
@@ -2051,7 +2327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12">
       <c r="B25" s="17" t="s">
         <v>32</v>
       </c>
@@ -2078,7 +2354,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12">
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
@@ -2107,7 +2383,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
@@ -2136,7 +2412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12">
       <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
@@ -2165,7 +2441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12">
       <c r="I29" s="3" t="s">
         <v>58</v>
       </c>
@@ -2173,32 +2449,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12">
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12">
       <c r="B31" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12">
       <c r="B32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:25">
       <c r="B33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:25">
       <c r="B35" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:25">
       <c r="B36" t="s">
         <v>65</v>
       </c>
@@ -2223,8 +2499,23 @@
       <c r="N36" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="U36" t="s">
+        <v>153</v>
+      </c>
+      <c r="V36" t="s">
+        <v>155</v>
+      </c>
+      <c r="W36" t="s">
+        <v>156</v>
+      </c>
+      <c r="X36" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25">
       <c r="B37" t="s">
         <v>71</v>
       </c>
@@ -2249,8 +2540,23 @@
       <c r="N37" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="U37" t="s">
+        <v>154</v>
+      </c>
+      <c r="V37" t="s">
+        <v>72</v>
+      </c>
+      <c r="W37" t="s">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25">
       <c r="B38" t="s">
         <v>78</v>
       </c>
@@ -2275,8 +2581,23 @@
       <c r="N38" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="U38" t="s">
+        <v>106</v>
+      </c>
+      <c r="V38" t="s">
+        <v>72</v>
+      </c>
+      <c r="W38" t="s">
+        <v>72</v>
+      </c>
+      <c r="X38" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25">
       <c r="B39" t="s">
         <v>82</v>
       </c>
@@ -2301,8 +2622,23 @@
       <c r="N39" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="U39" t="s">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s">
+        <v>72</v>
+      </c>
+      <c r="W39" t="s">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25">
       <c r="B40" t="s">
         <v>86</v>
       </c>
@@ -2315,8 +2651,23 @@
       <c r="F40" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="U40" t="s">
+        <v>71</v>
+      </c>
+      <c r="V40" t="s">
+        <v>72</v>
+      </c>
+      <c r="W40" t="s">
+        <v>72</v>
+      </c>
+      <c r="X40" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25">
       <c r="B41" t="s">
         <v>88</v>
       </c>
@@ -2329,8 +2680,11 @@
       <c r="F41" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="N41" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25">
       <c r="B42" t="s">
         <v>89</v>
       </c>
@@ -2344,57 +2698,57 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:25">
       <c r="B44" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:25">
       <c r="B45" s="20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:25">
       <c r="B46" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:25">
       <c r="B47" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:25">
       <c r="B48" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:27">
       <c r="B49" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:27">
       <c r="B50" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:27">
       <c r="B52" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:27">
       <c r="B53" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:27">
       <c r="B54" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:27">
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
         <v>130</v>
@@ -2403,7 +2757,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:27">
       <c r="B56" s="1" t="s">
         <v>136</v>
       </c>
@@ -2414,7 +2768,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:27">
       <c r="B57" s="1" t="s">
         <v>137</v>
       </c>
@@ -2425,7 +2779,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:27">
       <c r="B58" s="1" t="s">
         <v>140</v>
       </c>
@@ -2436,22 +2790,22 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:27">
       <c r="B59" s="19" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:27">
       <c r="B60" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:27">
       <c r="B62" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="2:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:27" ht="17.25" thickBot="1">
       <c r="B63" s="21" t="s">
         <v>150</v>
       </c>
@@ -2474,7 +2828,7 @@
       <c r="S63" s="21"/>
       <c r="T63" s="21"/>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:27">
       <c r="B64" s="22" t="s">
         <v>117</v>
       </c>
@@ -2527,7 +2881,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="2:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:27" ht="17.25" thickBot="1">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -2596,7 +2950,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="66" spans="2:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:27" ht="16.5" customHeight="1">
       <c r="B66" s="29" t="s">
         <v>91</v>
       </c>
@@ -2673,7 +3027,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:27">
       <c r="B67" s="35"/>
       <c r="C67" s="6" t="s">
         <v>95</v>
@@ -2748,7 +3102,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:27">
       <c r="B68" s="35"/>
       <c r="C68" s="6" t="s">
         <v>97</v>
@@ -2805,7 +3159,7 @@
         <v>0.23521480476804829</v>
       </c>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:27">
       <c r="B69" s="35"/>
       <c r="C69" s="6" t="s">
         <v>98</v>
@@ -2862,7 +3216,7 @@
         <v>0.68006909052999176</v>
       </c>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:27">
       <c r="B70" s="35"/>
       <c r="C70" s="6" t="s">
         <v>99</v>
@@ -2919,7 +3273,7 @@
         <v>0.27793144336080261</v>
       </c>
     </row>
-    <row r="71" spans="2:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:27" ht="17.25" thickBot="1">
       <c r="B71" s="37"/>
       <c r="C71" s="38" t="s">
         <v>100</v>
@@ -2972,7 +3326,7 @@
         <v>0.36953436233128767</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:27">
       <c r="B72" s="29" t="s">
         <v>92</v>
       </c>
@@ -3031,7 +3385,7 @@
         <v>0.20878281548720021</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:27">
       <c r="B73" s="35"/>
       <c r="C73" s="6" t="s">
         <v>95</v>
@@ -3088,7 +3442,7 @@
         <v>0.30433811408382672</v>
       </c>
     </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:27">
       <c r="B74" s="35"/>
       <c r="C74" s="6" t="s">
         <v>97</v>
@@ -3145,7 +3499,7 @@
         <v>0.241669849758085</v>
       </c>
     </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:27">
       <c r="B75" s="35"/>
       <c r="C75" s="6" t="s">
         <v>98</v>
@@ -3202,7 +3556,7 @@
         <v>0.67603124939991288</v>
       </c>
     </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:27">
       <c r="B76" s="35"/>
       <c r="C76" s="6" t="s">
         <v>99</v>
@@ -3259,7 +3613,7 @@
         <v>0.31587757001063449</v>
       </c>
     </row>
-    <row r="77" spans="2:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:27" ht="17.25" thickBot="1">
       <c r="B77" s="37"/>
       <c r="C77" s="38" t="s">
         <v>100</v>
@@ -3312,7 +3666,7 @@
         <v>0.34933991974793188</v>
       </c>
     </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:27">
       <c r="B78" s="29" t="s">
         <v>101</v>
       </c>
@@ -3371,7 +3725,7 @@
         <v>0.2336836588326161</v>
       </c>
     </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:27">
       <c r="B79" s="35"/>
       <c r="C79" s="6" t="s">
         <v>95</v>
@@ -3428,7 +3782,7 @@
         <v>0.25246203532908379</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:27">
       <c r="B80" s="35"/>
       <c r="C80" s="6" t="s">
         <v>97</v>
@@ -3485,7 +3839,7 @@
         <v>0.2229615657973866</v>
       </c>
     </row>
-    <row r="81" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:20">
       <c r="B81" s="35"/>
       <c r="C81" s="6" t="s">
         <v>98</v>
@@ -3542,7 +3896,7 @@
         <v>0.66673056374009465</v>
       </c>
     </row>
-    <row r="82" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:20">
       <c r="B82" s="35"/>
       <c r="C82" s="6" t="s">
         <v>99</v>
@@ -3599,7 +3953,7 @@
         <v>0.31583268516117879</v>
       </c>
     </row>
-    <row r="83" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:20" ht="17.25" thickBot="1">
       <c r="B83" s="37"/>
       <c r="C83" s="38" t="s">
         <v>100</v>
@@ -3652,9 +4006,9 @@
         <v>0.33833410177207196</v>
       </c>
     </row>
-    <row r="84" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:20" ht="17.25" thickBot="1">
       <c r="B84" s="21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C84" s="21"/>
       <c r="D84" s="21"/>
@@ -3671,11 +4025,8 @@
       <c r="O84" s="21"/>
       <c r="P84" s="21"/>
       <c r="Q84" s="21"/>
-      <c r="R84" s="21"/>
-      <c r="S84" s="21"/>
-      <c r="T84" s="21"/>
-    </row>
-    <row r="85" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="2:20">
       <c r="B85" s="22" t="s">
         <v>117</v>
       </c>
@@ -3693,21 +4044,18 @@
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="14" t="s">
+      <c r="I85" s="14" t="s">
         <v>111</v>
       </c>
+      <c r="J85" s="15"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="15"/>
+      <c r="L85" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="M85" s="15"/>
-      <c r="N85" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="O85" s="54"/>
-      <c r="P85" s="54"/>
-      <c r="Q85" s="55"/>
-    </row>
-    <row r="86" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N85" s="16"/>
+    </row>
+    <row r="86" spans="2:20" ht="17.25" thickBot="1">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -3721,35 +4069,26 @@
       <c r="H86" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I86" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="J86" s="26" t="s">
+      <c r="I86" s="26" t="s">
         <v>105</v>
       </c>
+      <c r="J86" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="K86" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="L86" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="M86" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="N86" s="50" t="s">
+      <c r="L86" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="O86" s="51" t="s">
+      <c r="M86" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="P86" s="51" t="s">
+      <c r="N86" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="Q86" s="52" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="87" spans="2:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="2:20">
       <c r="B87" s="29" t="s">
         <v>91</v>
       </c>
@@ -3763,43 +4102,34 @@
         <v>6.5217391304347797E-2</v>
       </c>
       <c r="F87" s="32">
-        <v>-8.3852987795748193E-2</v>
+        <v>-0.11</v>
       </c>
       <c r="G87" s="33">
-        <v>-3.9655772459538802E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="H87" s="33">
-        <v>-9.5844918359834302E-2</v>
-      </c>
-      <c r="I87" s="33">
-        <v>-5.4911708282958598E-2</v>
-      </c>
-      <c r="J87" s="32">
-        <v>5.5015568467247603E-2</v>
+        <v>-0.11</v>
+      </c>
+      <c r="I87" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="J87" s="33">
+        <v>0.06</v>
       </c>
       <c r="K87" s="33">
-        <v>6.9544204250746103E-2</v>
-      </c>
-      <c r="L87" s="33">
-        <v>6.3563971111282203E-2</v>
+        <v>0.06</v>
+      </c>
+      <c r="L87" s="32">
+        <v>0.17</v>
       </c>
       <c r="M87" s="33">
-        <v>6.4614388549277701E-2</v>
-      </c>
-      <c r="N87" s="32">
-        <v>0.1081021394064872</v>
-      </c>
-      <c r="O87" s="33">
-        <v>0.16631873642993719</v>
-      </c>
-      <c r="P87" s="33">
-        <v>0.20641437288842671</v>
-      </c>
-      <c r="Q87" s="34">
-        <v>0.18521888961534269</v>
-      </c>
-    </row>
-    <row r="88" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+      <c r="N87" s="33">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:20">
       <c r="B88" s="35"/>
       <c r="C88" s="6" t="s">
         <v>95</v>
@@ -3811,43 +4141,34 @@
         <v>2.8985507246376802E-2</v>
       </c>
       <c r="F88" s="7">
-        <v>0.11111674098375431</v>
+        <v>0.15</v>
       </c>
       <c r="G88" s="5">
-        <v>0.2801109093597402</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H88" s="5">
-        <v>0.23753224728440289</v>
-      </c>
-      <c r="I88" s="5">
-        <v>0.18136987315352859</v>
-      </c>
-      <c r="J88" s="7">
-        <v>0.19914532238299121</v>
+        <v>0.18</v>
+      </c>
+      <c r="I88" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="J88" s="5">
+        <v>0.23</v>
       </c>
       <c r="K88" s="5">
-        <v>0.2631070154982908</v>
-      </c>
-      <c r="L88" s="5">
-        <v>0.25044447851773322</v>
+        <v>0.25</v>
+      </c>
+      <c r="L88" s="7">
+        <v>0.42</v>
       </c>
       <c r="M88" s="5">
-        <v>0.27296873429944829</v>
-      </c>
-      <c r="N88" s="7">
-        <v>0.33115726865726869</v>
-      </c>
-      <c r="O88" s="5">
-        <v>0.52966107078039926</v>
-      </c>
-      <c r="P88" s="5">
-        <v>0.50343034730632974</v>
-      </c>
-      <c r="Q88" s="8">
-        <v>0.38774508173087591</v>
-      </c>
-    </row>
-    <row r="89" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.34</v>
+      </c>
+      <c r="N88" s="5">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="89" spans="2:20">
       <c r="B89" s="35"/>
       <c r="C89" s="6" t="s">
         <v>97</v>
@@ -3859,43 +4180,34 @@
         <v>0.14492753623188401</v>
       </c>
       <c r="F89" s="7">
-        <v>-1.8766488842823999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G89" s="5">
-        <v>0.16238319856239999</v>
+        <v>0</v>
       </c>
       <c r="H89" s="5">
-        <v>4.4334687831896702E-2</v>
-      </c>
-      <c r="I89" s="5">
-        <v>1.3256814195517001E-2</v>
-      </c>
-      <c r="J89" s="7">
-        <v>2.90696997151139E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="I89" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="J89" s="5">
+        <v>0.04</v>
       </c>
       <c r="K89" s="5">
-        <v>9.0836131849794902E-2</v>
-      </c>
-      <c r="L89" s="5">
-        <v>4.0822184452775301E-2</v>
+        <v>0.23</v>
+      </c>
+      <c r="L89" s="7">
+        <v>0.13</v>
       </c>
       <c r="M89" s="5">
-        <v>4.5762480922892403E-2</v>
-      </c>
-      <c r="N89" s="7">
-        <v>8.8391462938564397E-2</v>
-      </c>
-      <c r="O89" s="5">
-        <v>0.23627993565007621</v>
-      </c>
-      <c r="P89" s="5">
-        <v>0.14102440145381859</v>
-      </c>
-      <c r="Q89" s="8">
-        <v>0.1337117159735966</v>
-      </c>
-    </row>
-    <row r="90" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="N89" s="5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="90" spans="2:20">
       <c r="B90" s="35"/>
       <c r="C90" s="6" t="s">
         <v>98</v>
@@ -3907,43 +4219,34 @@
         <v>0.1884057971014492</v>
       </c>
       <c r="F90" s="7">
-        <v>7.4796835489211802E-2</v>
+        <v>0.53</v>
       </c>
       <c r="G90" s="5">
-        <v>0.4659537573381845</v>
+        <v>0.43</v>
       </c>
       <c r="H90" s="5">
-        <v>0.43208599057753527</v>
-      </c>
-      <c r="I90" s="5">
-        <v>0.52448655358757201</v>
-      </c>
-      <c r="J90" s="7">
-        <v>0.24415474984635721</v>
+        <v>0.6</v>
+      </c>
+      <c r="I90" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="J90" s="5">
+        <v>0.55629374204460691</v>
       </c>
       <c r="K90" s="5">
-        <v>0.55629374204460691</v>
-      </c>
-      <c r="L90" s="5">
-        <v>0.49049483207843181</v>
+        <v>0.67</v>
+      </c>
+      <c r="L90" s="7">
+        <v>0.71</v>
       </c>
       <c r="M90" s="5">
-        <v>0.47012211411131649</v>
-      </c>
-      <c r="N90" s="7">
-        <v>0.32400065434579461</v>
-      </c>
-      <c r="O90" s="5">
-        <v>0.69562617659575532</v>
-      </c>
-      <c r="P90" s="5">
-        <v>0.62412155818945581</v>
-      </c>
-      <c r="Q90" s="8">
-        <v>0.69549218901562082</v>
-      </c>
-    </row>
-    <row r="91" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.59</v>
+      </c>
+      <c r="N90" s="5">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="91" spans="2:20">
       <c r="B91" s="35"/>
       <c r="C91" s="6" t="s">
         <v>99</v>
@@ -3955,43 +4258,34 @@
         <v>5.0724637681159403E-2</v>
       </c>
       <c r="F91" s="7">
-        <v>-6.8404396589550004E-4</v>
+        <v>-0.04</v>
       </c>
       <c r="G91" s="5">
-        <v>0.1041319938677811</v>
+        <v>0.06</v>
       </c>
       <c r="H91" s="5">
-        <v>2.5078508757434701E-2</v>
-      </c>
-      <c r="I91" s="5">
-        <v>8.5561525041949693E-2</v>
-      </c>
-      <c r="J91" s="7">
-        <v>4.9622287884700501E-2</v>
+        <v>0.02</v>
+      </c>
+      <c r="I91" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="J91" s="5">
+        <v>0.1067799924887014</v>
       </c>
       <c r="K91" s="5">
-        <v>0.1067799924887014</v>
-      </c>
-      <c r="L91" s="5">
-        <v>6.1434211334869301E-2</v>
+        <v>0.06</v>
+      </c>
+      <c r="L91" s="7">
+        <v>0.12</v>
       </c>
       <c r="M91" s="5">
-        <v>7.4627139558084005E-2</v>
-      </c>
-      <c r="N91" s="7">
-        <v>0.19685479753770241</v>
-      </c>
-      <c r="O91" s="5">
-        <v>0.2574079611469548</v>
-      </c>
-      <c r="P91" s="5">
-        <v>0.2093384956873981</v>
-      </c>
-      <c r="Q91" s="8">
-        <v>0.22748991591530149</v>
-      </c>
-    </row>
-    <row r="92" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+      <c r="N91" s="5">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="92" spans="2:20" ht="17.25" thickBot="1">
       <c r="B92" s="37"/>
       <c r="C92" s="38" t="s">
         <v>100</v>
@@ -3999,43 +4293,43 @@
       <c r="D92" s="38"/>
       <c r="E92" s="39"/>
       <c r="F92" s="9">
-        <v>1.6522011173699683E-2</v>
-      </c>
-      <c r="G92" s="41">
-        <v>0.19458481733371341</v>
-      </c>
-      <c r="H92" s="10">
-        <v>0.12863730321828706</v>
-      </c>
-      <c r="I92" s="10">
-        <v>0.14995261153912173</v>
-      </c>
-      <c r="J92" s="9">
-        <v>0.11540152565928208</v>
+        <f>AVERAGE(F87:F91)</f>
+        <v>0.11000000000000001</v>
+      </c>
+      <c r="G92" s="10">
+        <f>AVERAGE(G87:G91)</f>
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H92" s="41">
+        <f>AVERAGE(H87:H91)</f>
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="I92" s="9">
+        <f>AVERAGE(I87:I91)</f>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="J92" s="10">
+        <f>AVERAGE(J87:J91)</f>
+        <v>0.19861474690666164</v>
       </c>
       <c r="K92" s="41">
-        <v>0.21731221722642804</v>
-      </c>
-      <c r="L92" s="10">
-        <v>0.18135193549901835</v>
+        <f>AVERAGE(K87:K91)</f>
+        <v>0.254</v>
+      </c>
+      <c r="L92" s="9">
+        <f>AVERAGE(L87:L91)</f>
+        <v>0.30999999999999994</v>
       </c>
       <c r="M92" s="10">
-        <v>0.18561897148820378</v>
-      </c>
-      <c r="N92" s="9">
-        <v>0.20970126457716348</v>
-      </c>
-      <c r="O92" s="41">
-        <v>0.37705877612062461</v>
-      </c>
-      <c r="P92" s="10">
-        <v>0.33686583510508578</v>
-      </c>
-      <c r="Q92" s="11">
-        <v>0.32593155845014754</v>
-      </c>
-    </row>
-    <row r="93" spans="2:20" x14ac:dyDescent="0.3">
+        <f>AVERAGE(M87:M91)</f>
+        <v>0.27599999999999997</v>
+      </c>
+      <c r="N92" s="41">
+        <f>AVERAGE(N87:N91)</f>
+        <v>0.33199999999999996</v>
+      </c>
+    </row>
+    <row r="93" spans="2:20">
       <c r="B93" s="29" t="s">
         <v>92</v>
       </c>
@@ -4049,43 +4343,34 @@
         <v>6.5217391304347797E-2</v>
       </c>
       <c r="F93" s="32">
-        <v>-3.8786086173473303E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="G93" s="33">
-        <v>2.00371169107952E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="H93" s="33">
-        <v>5.9160097433322102E-2</v>
-      </c>
-      <c r="I93" s="33">
-        <v>5.4929963703076103E-2</v>
-      </c>
-      <c r="J93" s="32">
-        <v>6.7531353395584498E-2</v>
+        <v>-0.16</v>
+      </c>
+      <c r="I93" s="32">
+        <v>0.08</v>
+      </c>
+      <c r="J93" s="33">
+        <v>0.06</v>
       </c>
       <c r="K93" s="33">
-        <v>7.9371599382373897E-2</v>
-      </c>
-      <c r="L93" s="33">
-        <v>8.4388010054681301E-2</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L93" s="32">
+        <v>0.11</v>
       </c>
       <c r="M93" s="33">
-        <v>0.1186329740095237</v>
-      </c>
-      <c r="N93" s="32">
-        <v>0.10393114080164439</v>
-      </c>
-      <c r="O93" s="33">
-        <v>0.22108976817494649</v>
-      </c>
-      <c r="P93" s="33">
-        <v>0.2353847755909611</v>
-      </c>
-      <c r="Q93" s="34">
-        <v>0.1791182501708817</v>
-      </c>
-    </row>
-    <row r="94" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.19</v>
+      </c>
+      <c r="N93" s="33">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="94" spans="2:20">
       <c r="B94" s="35"/>
       <c r="C94" s="6" t="s">
         <v>95</v>
@@ -4097,43 +4382,34 @@
         <v>2.8985507246376802E-2</v>
       </c>
       <c r="F94" s="7">
-        <v>0.2204501566386084</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G94" s="5">
-        <v>0.28248574107230762</v>
+        <v>0.27</v>
       </c>
       <c r="H94" s="5">
-        <v>0.3190742897085771</v>
-      </c>
-      <c r="I94" s="5">
-        <v>0.38840434597082718</v>
-      </c>
-      <c r="J94" s="7">
-        <v>0.31113044960942993</v>
+        <v>0.24</v>
+      </c>
+      <c r="I94" s="7">
+        <v>0.33</v>
+      </c>
+      <c r="J94" s="5">
+        <v>0.28000000000000003</v>
       </c>
       <c r="K94" s="5">
-        <v>0.35132293610952681</v>
-      </c>
-      <c r="L94" s="5">
-        <v>0.45350099421758938</v>
+        <v>0.44</v>
+      </c>
+      <c r="L94" s="7">
+        <v>0.48</v>
       </c>
       <c r="M94" s="5">
-        <v>0.47584101060724759</v>
-      </c>
-      <c r="N94" s="7">
-        <v>0.42475530915254511</v>
-      </c>
-      <c r="O94" s="5">
-        <v>0.50416698271908533</v>
-      </c>
-      <c r="P94" s="5">
-        <v>0.37919545680014199</v>
-      </c>
-      <c r="Q94" s="8">
-        <v>0.63331895857130172</v>
-      </c>
-    </row>
-    <row r="95" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.48</v>
+      </c>
+      <c r="N94" s="5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="95" spans="2:20">
       <c r="B95" s="35"/>
       <c r="C95" s="6" t="s">
         <v>97</v>
@@ -4145,43 +4421,34 @@
         <v>0.14492753623188401</v>
       </c>
       <c r="F95" s="7">
-        <v>9.5461362570380903E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G95" s="5">
-        <v>5.1701860594590997E-2</v>
+        <v>0.03</v>
       </c>
       <c r="H95" s="5">
-        <v>1.35488322756165E-2</v>
-      </c>
-      <c r="I95" s="5">
-        <v>4.2862147667648502E-2</v>
-      </c>
-      <c r="J95" s="7">
+        <v>-0.06</v>
+      </c>
+      <c r="I95" s="7">
         <v>4.8920377179727997E-2</v>
       </c>
+      <c r="J95" s="5">
+        <v>0.05</v>
+      </c>
       <c r="K95" s="5">
-        <v>6.8876450565475006E-2</v>
-      </c>
-      <c r="L95" s="5">
-        <v>5.6156657779508998E-2</v>
+        <v>0.09</v>
+      </c>
+      <c r="L95" s="7">
+        <v>0.14000000000000001</v>
       </c>
       <c r="M95" s="5">
-        <v>6.9875653866846799E-2</v>
-      </c>
-      <c r="N95" s="7">
-        <v>0.1727373476608956</v>
-      </c>
-      <c r="O95" s="5">
-        <v>0.13503094547097999</v>
-      </c>
-      <c r="P95" s="5">
-        <v>0.1070655361808777</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>0.1032663684532843</v>
-      </c>
-    </row>
-    <row r="96" spans="2:20" x14ac:dyDescent="0.3">
+        <v>0.12</v>
+      </c>
+      <c r="N95" s="5">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="96" spans="2:20">
       <c r="B96" s="35"/>
       <c r="C96" s="6" t="s">
         <v>98</v>
@@ -4193,43 +4460,34 @@
         <v>0.1884057971014492</v>
       </c>
       <c r="F96" s="7">
-        <v>0.4570866815111872</v>
+        <v>0.61</v>
       </c>
       <c r="G96" s="5">
-        <v>0.64317580576372624</v>
+        <v>0.67</v>
       </c>
       <c r="H96" s="5">
-        <v>0.4951699558212404</v>
-      </c>
-      <c r="I96" s="5">
-        <v>0.62902554472116723</v>
-      </c>
-      <c r="J96" s="7">
-        <v>0.40498547034513149</v>
+        <v>0.47</v>
+      </c>
+      <c r="I96" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J96" s="5">
+        <v>0.72</v>
       </c>
       <c r="K96" s="5">
-        <v>0.60006945199005235</v>
-      </c>
-      <c r="L96" s="5">
-        <v>0.48643249681963568</v>
+        <v>0.48</v>
+      </c>
+      <c r="L96" s="7">
+        <v>0.77</v>
       </c>
       <c r="M96" s="5">
-        <v>0.61876914690630636</v>
-      </c>
-      <c r="N96" s="7">
-        <v>0.72180246934790326</v>
-      </c>
-      <c r="O96" s="5">
-        <v>0.80882127846895169</v>
-      </c>
-      <c r="P96" s="5">
-        <v>0.70959056916967578</v>
-      </c>
-      <c r="Q96" s="8">
-        <v>0.80607233729154903</v>
-      </c>
-    </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.3">
+        <v>0.83</v>
+      </c>
+      <c r="N96" s="5">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
       <c r="B97" s="35"/>
       <c r="C97" s="6" t="s">
         <v>99</v>
@@ -4241,43 +4499,34 @@
         <v>5.0724637681159403E-2</v>
       </c>
       <c r="F97" s="7">
-        <v>9.6090909119169003E-3</v>
+        <v>0.04</v>
       </c>
       <c r="G97" s="5">
-        <v>6.6668166107890003E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="H97" s="5">
-        <v>-1.6466880673519601E-2</v>
-      </c>
-      <c r="I97" s="5">
-        <v>7.1717164219125704E-2</v>
-      </c>
-      <c r="J97" s="7">
-        <v>6.9311933881791493E-2</v>
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="I97" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="J97" s="5">
+        <v>0.06</v>
       </c>
       <c r="K97" s="5">
-        <v>7.9542315874862504E-2</v>
-      </c>
-      <c r="L97" s="5">
-        <v>7.3498535637566406E-2</v>
+        <v>0.04</v>
+      </c>
+      <c r="L97" s="7">
+        <v>0.18</v>
       </c>
       <c r="M97" s="5">
-        <v>8.8594287694729407E-2</v>
-      </c>
-      <c r="N97" s="7">
-        <v>0.13281915435557809</v>
-      </c>
-      <c r="O97" s="5">
-        <v>0.21831176745636799</v>
-      </c>
-      <c r="P97" s="5">
-        <v>0.16164551239401539</v>
-      </c>
-      <c r="Q97" s="8">
-        <v>0.2231909469840504</v>
-      </c>
-    </row>
-    <row r="98" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.12</v>
+      </c>
+      <c r="N97" s="5">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" ht="17.25" thickBot="1">
       <c r="B98" s="37"/>
       <c r="C98" s="38" t="s">
         <v>100</v>
@@ -4285,43 +4534,43 @@
       <c r="D98" s="38"/>
       <c r="E98" s="39"/>
       <c r="F98" s="9">
-        <v>0.14876424109172401</v>
+        <f>AVERAGE(F93:F97)</f>
+        <v>0.186</v>
       </c>
       <c r="G98" s="10">
-        <v>0.21281373808986198</v>
-      </c>
-      <c r="H98" s="10">
-        <v>0.17409725891304728</v>
-      </c>
-      <c r="I98" s="41">
-        <v>0.23738783325636895</v>
-      </c>
-      <c r="J98" s="9">
-        <v>0.18037591688233306</v>
-      </c>
-      <c r="K98" s="10">
-        <v>0.23583655078445812</v>
-      </c>
-      <c r="L98" s="10">
-        <v>0.23079533890179635</v>
-      </c>
-      <c r="M98" s="41">
-        <v>0.27434261461693077</v>
-      </c>
-      <c r="N98" s="9">
-        <v>0.3112090842637133</v>
-      </c>
-      <c r="O98" s="10">
-        <v>0.37748414845806633</v>
-      </c>
-      <c r="P98" s="10">
-        <v>0.3185763700271344</v>
-      </c>
-      <c r="Q98" s="47">
-        <v>0.38899337229421349</v>
-      </c>
-    </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.3">
+        <f>AVERAGE(G93:G97)</f>
+        <v>0.186</v>
+      </c>
+      <c r="H98" s="41">
+        <f>AVERAGE(H93:H97)</f>
+        <v>4.1999999999999996E-2</v>
+      </c>
+      <c r="I98" s="9">
+        <f>AVERAGE(I93:I97)</f>
+        <v>0.21978407543594561</v>
+      </c>
+      <c r="J98" s="10">
+        <f>AVERAGE(J93:J97)</f>
+        <v>0.23399999999999999</v>
+      </c>
+      <c r="K98" s="41">
+        <f>AVERAGE(K93:K97)</f>
+        <v>0.22400000000000003</v>
+      </c>
+      <c r="L98" s="9">
+        <f>AVERAGE(L93:L97)</f>
+        <v>0.33599999999999997</v>
+      </c>
+      <c r="M98" s="10">
+        <f>AVERAGE(M93:M97)</f>
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="N98" s="41">
+        <f>AVERAGE(N93:N97)</f>
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17">
       <c r="B99" s="29" t="s">
         <v>101</v>
       </c>
@@ -4335,43 +4584,34 @@
         <v>6.5217391304347797E-2</v>
       </c>
       <c r="F99" s="32">
-        <v>-1.37293528683901E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="G99" s="33">
-        <v>-0.10540960290521301</v>
+        <v>-0.03</v>
       </c>
       <c r="H99" s="33">
-        <v>-7.6167816664092405E-2</v>
-      </c>
-      <c r="I99" s="33">
-        <v>4.3814197611345897E-2</v>
-      </c>
-      <c r="J99" s="32">
-        <v>0.106206508276523</v>
+        <v>-0.1</v>
+      </c>
+      <c r="I99" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="J99" s="33">
+        <v>0.06</v>
       </c>
       <c r="K99" s="33">
-        <v>5.3302310692446203E-2</v>
-      </c>
-      <c r="L99" s="33">
-        <v>6.01253221878746E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="L99" s="32">
+        <v>0.18</v>
       </c>
       <c r="M99" s="33">
-        <v>8.8111977440462105E-2</v>
-      </c>
-      <c r="N99" s="32">
-        <v>0.14440376793317969</v>
-      </c>
-      <c r="O99" s="33">
-        <v>0.19935844788384069</v>
-      </c>
-      <c r="P99" s="33">
-        <v>5.0120772946859897E-2</v>
-      </c>
-      <c r="Q99" s="34">
-        <v>0.22231585460925779</v>
-      </c>
-    </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.3">
+        <v>0.16</v>
+      </c>
+      <c r="N99" s="33">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
       <c r="B100" s="35"/>
       <c r="C100" s="6" t="s">
         <v>95</v>
@@ -4383,43 +4623,34 @@
         <v>2.8985507246376802E-2</v>
       </c>
       <c r="F100" s="7">
-        <v>0.2449390044497595</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="5">
-        <v>0.31782197948522511</v>
+        <v>0.18</v>
       </c>
       <c r="H100" s="5">
-        <v>0.37469588221812611</v>
-      </c>
-      <c r="I100" s="5">
-        <v>0.38010350927102837</v>
-      </c>
-      <c r="J100" s="7">
-        <v>0.27588990364014421</v>
+        <v>0.3</v>
+      </c>
+      <c r="I100" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="J100" s="5">
+        <v>0.28000000000000003</v>
       </c>
       <c r="K100" s="5">
-        <v>0.32762517404119601</v>
-      </c>
-      <c r="L100" s="5">
-        <v>0.39097380471190601</v>
+        <v>0.43</v>
+      </c>
+      <c r="L100" s="7">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M100" s="5">
-        <v>0.36051157011691348</v>
-      </c>
-      <c r="N100" s="7">
-        <v>0.5081655420242116</v>
-      </c>
-      <c r="O100" s="5">
-        <v>0.57748118796846803</v>
-      </c>
-      <c r="P100" s="5">
-        <v>0.56284400260715972</v>
-      </c>
-      <c r="Q100" s="8">
-        <v>0.60832340439586807</v>
-      </c>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.3">
+        <v>0.41</v>
+      </c>
+      <c r="N100" s="5">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
       <c r="B101" s="35"/>
       <c r="C101" s="6" t="s">
         <v>97</v>
@@ -4431,43 +4662,34 @@
         <v>0.14492753623188401</v>
       </c>
       <c r="F101" s="7">
-        <v>9.4263370089226806E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G101" s="5">
-        <v>0.15957805213997139</v>
+        <v>-0.02</v>
       </c>
       <c r="H101" s="5">
-        <v>-1.0550946190508E-2</v>
-      </c>
-      <c r="I101" s="5">
-        <v>6.4579444589532103E-2</v>
-      </c>
-      <c r="J101" s="7">
-        <v>0.1332734549267339</v>
+        <v>0.03</v>
+      </c>
+      <c r="I101" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="J101" s="5">
+        <v>0.04</v>
       </c>
       <c r="K101" s="5">
-        <v>6.00433424523956E-2</v>
-      </c>
-      <c r="L101" s="5">
-        <v>5.4898440464819398E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="L101" s="7">
+        <v>0.13</v>
       </c>
       <c r="M101" s="5">
-        <v>5.3488880143233601E-2</v>
-      </c>
-      <c r="N101" s="7">
-        <v>0.16534391534391529</v>
-      </c>
-      <c r="O101" s="5">
-        <v>0.22257601835915089</v>
-      </c>
-      <c r="P101" s="5">
-        <v>7.6128484760941695E-2</v>
-      </c>
-      <c r="Q101" s="8">
-        <v>0.15548472413485029</v>
-      </c>
-    </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.3">
+        <v>0.08</v>
+      </c>
+      <c r="N101" s="5">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
       <c r="B102" s="35"/>
       <c r="C102" s="6" t="s">
         <v>98</v>
@@ -4479,43 +4701,34 @@
         <v>0.1884057971014492</v>
       </c>
       <c r="F102" s="7">
-        <v>0.36399765051157551</v>
+        <v>0.61</v>
       </c>
       <c r="G102" s="5">
-        <v>0.62256923945283416</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H102" s="5">
-        <v>0.57126248800364121</v>
-      </c>
-      <c r="I102" s="5">
-        <v>0.53654385012449213</v>
-      </c>
-      <c r="J102" s="7">
-        <v>0.43211204083057497</v>
+        <v>0.6</v>
+      </c>
+      <c r="I102" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="J102" s="5">
+        <v>0.62</v>
       </c>
       <c r="K102" s="5">
-        <v>0.56640214195500771</v>
-      </c>
-      <c r="L102" s="5">
-        <v>0.58566836533529909</v>
+        <v>0.53</v>
+      </c>
+      <c r="L102" s="7">
+        <v>0.79</v>
       </c>
       <c r="M102" s="5">
-        <v>0.5649804413614824</v>
-      </c>
-      <c r="N102" s="7">
-        <v>0.58761899478372315</v>
-      </c>
-      <c r="O102" s="5">
-        <v>0.81184607968002642</v>
-      </c>
-      <c r="P102" s="5">
-        <v>0.77016890262157633</v>
-      </c>
-      <c r="Q102" s="8">
-        <v>0.73829246091240097</v>
-      </c>
-    </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.3">
+        <v>0.72</v>
+      </c>
+      <c r="N102" s="5">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
       <c r="B103" s="35"/>
       <c r="C103" s="6" t="s">
         <v>99</v>
@@ -4527,102 +4740,2676 @@
         <v>5.0724637681159403E-2</v>
       </c>
       <c r="F103" s="7">
-        <v>9.0873256876832897E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G103" s="5">
-        <v>-7.2669713659328002E-3</v>
+        <v>-0.04</v>
       </c>
       <c r="H103" s="5">
-        <v>0.1074382213188757</v>
-      </c>
-      <c r="I103" s="5">
-        <v>0.1133115677139481</v>
-      </c>
-      <c r="J103" s="7">
-        <v>0.14391609274123679</v>
+        <v>-0.17</v>
+      </c>
+      <c r="I103" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="J103" s="5">
+        <v>0.06</v>
       </c>
       <c r="K103" s="5">
-        <v>5.66250373030069E-2</v>
-      </c>
-      <c r="L103" s="5">
-        <v>9.0533781729550303E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="L103" s="7">
+        <v>0.21</v>
       </c>
       <c r="M103" s="5">
-        <v>0.1508813651521474</v>
-      </c>
-      <c r="N103" s="7">
-        <v>0.2145976949103475</v>
-      </c>
-      <c r="O103" s="5">
-        <v>0.18591184806389291</v>
-      </c>
-      <c r="P103" s="5">
-        <v>0.261208020136734</v>
-      </c>
-      <c r="Q103" s="8">
-        <v>0.2437281908051368</v>
-      </c>
-    </row>
-    <row r="104" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.11</v>
+      </c>
+      <c r="N103" s="5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17" ht="17.25" thickBot="1">
       <c r="B104" s="37"/>
       <c r="C104" s="38" t="s">
         <v>100</v>
       </c>
       <c r="D104" s="38"/>
       <c r="E104" s="39"/>
-      <c r="F104" s="9">
+      <c r="F104" s="77">
+        <f>AVERAGE(F99:F103)</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="G104" s="10">
+        <f>AVERAGE(G99:G103)</f>
+        <v>0.13</v>
+      </c>
+      <c r="H104" s="10">
+        <f>AVERAGE(H99:H103)</f>
+        <v>0.13199999999999998</v>
+      </c>
+      <c r="I104" s="77">
+        <f>AVERAGE(I99:I103)</f>
+        <v>0.24400000000000005</v>
+      </c>
+      <c r="J104" s="10">
+        <f>AVERAGE(J99:J103)</f>
+        <v>0.21200000000000002</v>
+      </c>
+      <c r="K104" s="41">
+        <f>AVERAGE(K99:K103)</f>
+        <v>0.22200000000000003</v>
+      </c>
+      <c r="L104" s="77">
+        <f>AVERAGE(L99:L103)</f>
+        <v>0.374</v>
+      </c>
+      <c r="M104" s="10">
+        <f>AVERAGE(M99:M103)</f>
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="N104" s="10">
+        <f>AVERAGE(N99:N103)</f>
+        <v>0.33999999999999997</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B105" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C105" s="21"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="21"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="21"/>
+      <c r="J105" s="21"/>
+      <c r="K105" s="21"/>
+      <c r="L105" s="21"/>
+      <c r="M105" s="21"/>
+      <c r="N105" s="21"/>
+      <c r="O105" s="21"/>
+      <c r="P105" s="21"/>
+      <c r="Q105" s="21"/>
+    </row>
+    <row r="106" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B106" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D106" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="K106" s="15"/>
+      <c r="L106" s="15"/>
+      <c r="M106" s="15"/>
+      <c r="N106" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="O106" s="54"/>
+      <c r="P106" s="54"/>
+      <c r="Q106" s="55"/>
+    </row>
+    <row r="107" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B107" s="24"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="25"/>
+      <c r="E107" s="46"/>
+      <c r="F107" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H107" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I107" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="J107" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="K107" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="L107" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="M107" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="N107" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="O107" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="P107" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q107" s="52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
+      <c r="B108" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C108" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D108" s="30">
+        <v>9</v>
+      </c>
+      <c r="E108" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F108" s="32">
+        <v>-8.3852987795748193E-2</v>
+      </c>
+      <c r="G108" s="33">
+        <v>-3.9655772459538802E-2</v>
+      </c>
+      <c r="H108" s="33">
+        <v>-0.03</v>
+      </c>
+      <c r="I108" s="33">
+        <v>-5.4911708282958598E-2</v>
+      </c>
+      <c r="J108" s="32">
+        <v>5.5015568467247603E-2</v>
+      </c>
+      <c r="K108" s="33">
+        <v>6.9544204250746103E-2</v>
+      </c>
+      <c r="L108" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="M108" s="33">
+        <v>6.4614388549277701E-2</v>
+      </c>
+      <c r="N108" s="32">
+        <v>0.1081021394064872</v>
+      </c>
+      <c r="O108" s="33">
+        <v>0.16631873642993719</v>
+      </c>
+      <c r="P108" s="33">
+        <v>0.24</v>
+      </c>
+      <c r="Q108" s="34">
+        <v>0.18521888961534269</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
+      <c r="B109" s="35"/>
+      <c r="C109" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109" s="6">
+        <v>4</v>
+      </c>
+      <c r="E109" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F109" s="7">
+        <v>0.11111674098375431</v>
+      </c>
+      <c r="G109" s="5">
+        <v>0.2801109093597402</v>
+      </c>
+      <c r="H109" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="I109" s="5">
+        <v>0.18136987315352859</v>
+      </c>
+      <c r="J109" s="7">
+        <v>0.19914532238299121</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0.2631070154982908</v>
+      </c>
+      <c r="L109" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="M109" s="5">
+        <v>0.27296873429944829</v>
+      </c>
+      <c r="N109" s="7">
+        <v>0.33115726865726869</v>
+      </c>
+      <c r="O109" s="5">
+        <v>0.52966107078039926</v>
+      </c>
+      <c r="P109" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>0.38774508173087591</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
+      <c r="B110" s="35"/>
+      <c r="C110" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D110" s="6">
+        <v>20</v>
+      </c>
+      <c r="E110" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F110" s="7">
+        <v>-1.8766488842823999E-2</v>
+      </c>
+      <c r="G110" s="5">
+        <v>0.16238319856239999</v>
+      </c>
+      <c r="H110" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="I110" s="5">
+        <v>1.3256814195517001E-2</v>
+      </c>
+      <c r="J110" s="7">
+        <v>2.90696997151139E-2</v>
+      </c>
+      <c r="K110" s="5">
+        <v>9.0836131849794902E-2</v>
+      </c>
+      <c r="L110" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="M110" s="5">
+        <v>4.5762480922892403E-2</v>
+      </c>
+      <c r="N110" s="7">
+        <v>8.8391462938564397E-2</v>
+      </c>
+      <c r="O110" s="5">
+        <v>0.23627993565007621</v>
+      </c>
+      <c r="P110" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="Q110" s="8">
+        <v>0.1337117159735966</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
+      <c r="B111" s="35"/>
+      <c r="C111" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D111" s="6">
+        <v>26</v>
+      </c>
+      <c r="E111" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F111" s="7">
+        <v>7.4796835489211802E-2</v>
+      </c>
+      <c r="G111" s="5">
+        <v>0.4659537573381845</v>
+      </c>
+      <c r="H111" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="I111" s="5">
+        <v>0.52448655358757201</v>
+      </c>
+      <c r="J111" s="7">
+        <v>0.24415474984635721</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0.55629374204460691</v>
+      </c>
+      <c r="L111" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="M111" s="5">
+        <v>0.47012211411131649</v>
+      </c>
+      <c r="N111" s="7">
+        <v>0.32400065434579461</v>
+      </c>
+      <c r="O111" s="5">
+        <v>0.69562617659575532</v>
+      </c>
+      <c r="P111" s="5">
+        <v>0.66</v>
+      </c>
+      <c r="Q111" s="8">
+        <v>0.69549218901562082</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
+      <c r="B112" s="35"/>
+      <c r="C112" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D112" s="6">
+        <v>7</v>
+      </c>
+      <c r="E112" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F112" s="7">
+        <v>-6.8404396589550004E-4</v>
+      </c>
+      <c r="G112" s="5">
+        <v>0.1041319938677811</v>
+      </c>
+      <c r="H112" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I112" s="5">
+        <v>8.5561525041949693E-2</v>
+      </c>
+      <c r="J112" s="7">
+        <v>4.9622287884700501E-2</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0.1067799924887014</v>
+      </c>
+      <c r="L112" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M112" s="5">
+        <v>7.4627139558084005E-2</v>
+      </c>
+      <c r="N112" s="7">
+        <v>0.19685479753770241</v>
+      </c>
+      <c r="O112" s="5">
+        <v>0.2574079611469548</v>
+      </c>
+      <c r="P112" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="Q112" s="8">
+        <v>0.22748991591530149</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B113" s="37"/>
+      <c r="C113" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113" s="38"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="9">
+        <v>1.6522011173699683E-2</v>
+      </c>
+      <c r="G113" s="41">
+        <v>0.19458481733371341</v>
+      </c>
+      <c r="H113" s="10">
+        <f>AVERAGE(H108:H112)</f>
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I113" s="10">
+        <v>0.14995261153912173</v>
+      </c>
+      <c r="J113" s="9">
+        <v>0.11540152565928208</v>
+      </c>
+      <c r="K113" s="41">
+        <v>0.21731221722642804</v>
+      </c>
+      <c r="L113" s="10">
+        <f>AVERAGE(L108:L112)</f>
+        <v>0.192</v>
+      </c>
+      <c r="M113" s="10">
+        <v>0.18561897148820378</v>
+      </c>
+      <c r="N113" s="9">
+        <v>0.20970126457716348</v>
+      </c>
+      <c r="O113" s="41">
+        <v>0.37705877612062461</v>
+      </c>
+      <c r="P113" s="10">
+        <f>AVERAGE(P108:P112)</f>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="Q113" s="11">
+        <v>0.32593155845014754</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
+      <c r="B114" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C114" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D114" s="30">
+        <v>9</v>
+      </c>
+      <c r="E114" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F114" s="32">
+        <v>-3.8786086173473303E-2</v>
+      </c>
+      <c r="G114" s="33">
+        <v>2.00371169107952E-2</v>
+      </c>
+      <c r="H114" s="33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I114" s="33">
+        <v>5.4929963703076103E-2</v>
+      </c>
+      <c r="J114" s="32">
+        <v>6.7531353395584498E-2</v>
+      </c>
+      <c r="K114" s="33">
+        <v>7.9371599382373897E-2</v>
+      </c>
+      <c r="L114" s="33">
+        <v>0.09</v>
+      </c>
+      <c r="M114" s="33">
+        <v>0.1186329740095237</v>
+      </c>
+      <c r="N114" s="32">
+        <v>0.10393114080164439</v>
+      </c>
+      <c r="O114" s="33">
+        <v>0.22108976817494649</v>
+      </c>
+      <c r="P114" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="Q114" s="34">
+        <v>0.1791182501708817</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
+      <c r="B115" s="35"/>
+      <c r="C115" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D115" s="6">
+        <v>4</v>
+      </c>
+      <c r="E115" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F115" s="7">
+        <v>0.2204501566386084</v>
+      </c>
+      <c r="G115" s="5">
+        <v>0.28248574107230762</v>
+      </c>
+      <c r="H115" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="I115" s="5">
+        <v>0.38840434597082718</v>
+      </c>
+      <c r="J115" s="7">
+        <v>0.31113044960942993</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0.35132293610952681</v>
+      </c>
+      <c r="L115" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="M115" s="5">
+        <v>0.47584101060724759</v>
+      </c>
+      <c r="N115" s="7">
+        <v>0.42475530915254511</v>
+      </c>
+      <c r="O115" s="5">
+        <v>0.50416698271908533</v>
+      </c>
+      <c r="P115" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>0.63331895857130172</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
+      <c r="B116" s="35"/>
+      <c r="C116" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D116" s="6">
+        <v>20</v>
+      </c>
+      <c r="E116" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F116" s="7">
+        <v>9.5461362570380903E-2</v>
+      </c>
+      <c r="G116" s="5">
+        <v>5.1701860594590997E-2</v>
+      </c>
+      <c r="H116" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="I116" s="5">
+        <v>4.2862147667648502E-2</v>
+      </c>
+      <c r="J116" s="7">
+        <v>4.8920377179727997E-2</v>
+      </c>
+      <c r="K116" s="5">
+        <v>6.8876450565475006E-2</v>
+      </c>
+      <c r="L116" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="M116" s="5">
+        <v>6.9875653866846799E-2</v>
+      </c>
+      <c r="N116" s="7">
+        <v>0.1727373476608956</v>
+      </c>
+      <c r="O116" s="5">
+        <v>0.13503094547097999</v>
+      </c>
+      <c r="P116" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>0.1032663684532843</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17">
+      <c r="B117" s="35"/>
+      <c r="C117" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D117" s="6">
+        <v>26</v>
+      </c>
+      <c r="E117" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F117" s="7">
+        <v>0.4570866815111872</v>
+      </c>
+      <c r="G117" s="5">
+        <v>0.64317580576372624</v>
+      </c>
+      <c r="H117" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I117" s="5">
+        <v>0.62902554472116723</v>
+      </c>
+      <c r="J117" s="7">
+        <v>0.40498547034513149</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0.60006945199005235</v>
+      </c>
+      <c r="L117" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="M117" s="5">
+        <v>0.61876914690630636</v>
+      </c>
+      <c r="N117" s="7">
+        <v>0.72180246934790326</v>
+      </c>
+      <c r="O117" s="5">
+        <v>0.80882127846895169</v>
+      </c>
+      <c r="P117" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>0.80607233729154903</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
+      <c r="B118" s="35"/>
+      <c r="C118" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D118" s="6">
+        <v>7</v>
+      </c>
+      <c r="E118" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F118" s="7">
+        <v>9.6090909119169003E-3</v>
+      </c>
+      <c r="G118" s="5">
+        <v>6.6668166107890003E-2</v>
+      </c>
+      <c r="H118" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="I118" s="5">
+        <v>7.1717164219125704E-2</v>
+      </c>
+      <c r="J118" s="7">
+        <v>6.9311933881791493E-2</v>
+      </c>
+      <c r="K118" s="5">
+        <v>7.9542315874862504E-2</v>
+      </c>
+      <c r="L118" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="M118" s="5">
+        <v>8.8594287694729407E-2</v>
+      </c>
+      <c r="N118" s="7">
+        <v>0.13281915435557809</v>
+      </c>
+      <c r="O118" s="5">
+        <v>0.21831176745636799</v>
+      </c>
+      <c r="P118" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>0.2231909469840504</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B119" s="37"/>
+      <c r="C119" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D119" s="38"/>
+      <c r="E119" s="39"/>
+      <c r="F119" s="9">
+        <v>0.14876424109172401</v>
+      </c>
+      <c r="G119" s="10">
+        <v>0.21281373808986198</v>
+      </c>
+      <c r="H119" s="10">
+        <f>AVERAGE(H114:H118)</f>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="I119" s="41">
+        <v>0.23738783325636895</v>
+      </c>
+      <c r="J119" s="9">
+        <v>0.18037591688233306</v>
+      </c>
+      <c r="K119" s="10">
+        <v>0.23583655078445812</v>
+      </c>
+      <c r="L119" s="41">
+        <f>AVERAGE(L114:L118)</f>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="M119" s="10">
+        <v>0.27434261461693077</v>
+      </c>
+      <c r="N119" s="9">
+        <v>0.3112090842637133</v>
+      </c>
+      <c r="O119" s="10">
+        <v>0.37748414845806633</v>
+      </c>
+      <c r="P119" s="41">
+        <f>AVERAGE(P114:P118)</f>
+        <v>0.39</v>
+      </c>
+      <c r="Q119" s="47">
+        <v>0.38899337229421349</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
+      <c r="B120" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C120" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D120" s="30">
+        <v>9</v>
+      </c>
+      <c r="E120" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F120" s="32">
+        <v>-1.37293528683901E-2</v>
+      </c>
+      <c r="G120" s="33">
+        <v>-0.10540960290521301</v>
+      </c>
+      <c r="H120" s="33">
+        <v>-0.04</v>
+      </c>
+      <c r="I120" s="33">
+        <v>4.3814197611345897E-2</v>
+      </c>
+      <c r="J120" s="32">
+        <v>0.106206508276523</v>
+      </c>
+      <c r="K120" s="33">
+        <v>5.3302310692446203E-2</v>
+      </c>
+      <c r="L120" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="M120" s="33">
+        <v>8.8111977440462105E-2</v>
+      </c>
+      <c r="N120" s="32">
+        <v>0.14440376793317969</v>
+      </c>
+      <c r="O120" s="33">
+        <v>0.19935844788384069</v>
+      </c>
+      <c r="P120" s="33">
+        <v>0.18</v>
+      </c>
+      <c r="Q120" s="34">
+        <v>0.22231585460925779</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
+      <c r="B121" s="35"/>
+      <c r="C121" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D121" s="6">
+        <v>4</v>
+      </c>
+      <c r="E121" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F121" s="7">
+        <v>0.2449390044497595</v>
+      </c>
+      <c r="G121" s="5">
+        <v>0.31782197948522511</v>
+      </c>
+      <c r="H121" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="I121" s="5">
+        <v>0.38010350927102837</v>
+      </c>
+      <c r="J121" s="7">
+        <v>0.27588990364014421</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0.32762517404119601</v>
+      </c>
+      <c r="L121" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="M121" s="5">
+        <v>0.36051157011691348</v>
+      </c>
+      <c r="N121" s="7">
+        <v>0.5081655420242116</v>
+      </c>
+      <c r="O121" s="5">
+        <v>0.57748118796846803</v>
+      </c>
+      <c r="P121" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>0.60832340439586807</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
+      <c r="B122" s="35"/>
+      <c r="C122" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D122" s="6">
+        <v>20</v>
+      </c>
+      <c r="E122" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F122" s="7">
+        <v>9.4263370089226806E-2</v>
+      </c>
+      <c r="G122" s="5">
+        <v>0.15957805213997139</v>
+      </c>
+      <c r="H122" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I122" s="5">
+        <v>6.4579444589532103E-2</v>
+      </c>
+      <c r="J122" s="7">
+        <v>0.1332734549267339</v>
+      </c>
+      <c r="K122" s="5">
+        <v>6.00433424523956E-2</v>
+      </c>
+      <c r="L122" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="M122" s="5">
+        <v>5.3488880143233601E-2</v>
+      </c>
+      <c r="N122" s="7">
+        <v>0.16534391534391529</v>
+      </c>
+      <c r="O122" s="5">
+        <v>0.22257601835915089</v>
+      </c>
+      <c r="P122" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>0.15548472413485029</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
+      <c r="B123" s="35"/>
+      <c r="C123" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D123" s="6">
+        <v>26</v>
+      </c>
+      <c r="E123" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F123" s="7">
+        <v>0.36399765051157551</v>
+      </c>
+      <c r="G123" s="5">
+        <v>0.62256923945283416</v>
+      </c>
+      <c r="H123" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="I123" s="5">
+        <v>0.53654385012449213</v>
+      </c>
+      <c r="J123" s="7">
+        <v>0.43211204083057497</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0.56640214195500771</v>
+      </c>
+      <c r="L123" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M123" s="5">
+        <v>0.5649804413614824</v>
+      </c>
+      <c r="N123" s="7">
+        <v>0.58761899478372315</v>
+      </c>
+      <c r="O123" s="5">
+        <v>0.81184607968002642</v>
+      </c>
+      <c r="P123" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="Q123" s="8">
+        <v>0.73829246091240097</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
+      <c r="B124" s="35"/>
+      <c r="C124" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D124" s="6">
+        <v>7</v>
+      </c>
+      <c r="E124" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F124" s="7">
+        <v>9.0873256876832897E-2</v>
+      </c>
+      <c r="G124" s="5">
+        <v>-7.2669713659328002E-3</v>
+      </c>
+      <c r="H124" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I124" s="5">
+        <v>0.1133115677139481</v>
+      </c>
+      <c r="J124" s="7">
+        <v>0.14391609274123679</v>
+      </c>
+      <c r="K124" s="5">
+        <v>5.66250373030069E-2</v>
+      </c>
+      <c r="L124" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="M124" s="5">
+        <v>0.1508813651521474</v>
+      </c>
+      <c r="N124" s="7">
+        <v>0.2145976949103475</v>
+      </c>
+      <c r="O124" s="5">
+        <v>0.18591184806389291</v>
+      </c>
+      <c r="P124" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>0.2437281908051368</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B125" s="37"/>
+      <c r="C125" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D125" s="38"/>
+      <c r="E125" s="39"/>
+      <c r="F125" s="9">
         <v>0.15606878581180092</v>
       </c>
-      <c r="G104" s="10">
+      <c r="G125" s="10">
         <v>0.19745853936137697</v>
       </c>
-      <c r="H104" s="10">
-        <v>0.1933355657372085</v>
-      </c>
-      <c r="I104" s="41">
+      <c r="H125" s="10">
+        <f>AVERAGE(H120:H124)</f>
+        <v>0.184</v>
+      </c>
+      <c r="I125" s="41">
         <v>0.2276705138620693</v>
       </c>
-      <c r="J104" s="9">
+      <c r="J125" s="9">
         <v>0.21827960008304256</v>
       </c>
-      <c r="K104" s="10">
+      <c r="K125" s="10">
         <v>0.21279960128881048</v>
       </c>
-      <c r="L104" s="41">
-        <v>0.23643994288588988</v>
-      </c>
-      <c r="M104" s="41">
+      <c r="L125" s="10">
+        <f>AVERAGE(L120:L124)</f>
+        <v>0.24200000000000005</v>
+      </c>
+      <c r="M125" s="41">
         <v>0.2435948468428478</v>
       </c>
-      <c r="N104" s="9">
+      <c r="N125" s="9">
         <v>0.32402598299907542</v>
       </c>
-      <c r="O104" s="41">
+      <c r="O125" s="41">
         <v>0.39943471639107575</v>
       </c>
-      <c r="P104" s="10">
-        <v>0.34409403661465432</v>
-      </c>
-      <c r="Q104" s="11">
+      <c r="P125" s="10">
+        <f>AVERAGE(P120:P124)</f>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="Q125" s="11">
         <v>0.39362892697150281</v>
       </c>
     </row>
+    <row r="126" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B126" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" s="21"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="44"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="21"/>
+      <c r="I126" s="21"/>
+      <c r="J126" s="21"/>
+      <c r="K126" s="21"/>
+      <c r="L126" s="21"/>
+      <c r="M126" s="21"/>
+      <c r="N126" s="21"/>
+      <c r="O126" s="21"/>
+      <c r="P126" s="21"/>
+      <c r="Q126" s="21"/>
+    </row>
+    <row r="127" spans="2:17">
+      <c r="B127" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D127" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E127" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G127" s="15"/>
+      <c r="H127" s="15"/>
+      <c r="I127" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J127" s="15"/>
+      <c r="K127" s="15"/>
+      <c r="L127" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="M127" s="15"/>
+      <c r="N127" s="16"/>
+      <c r="O127" s="21"/>
+      <c r="P127" s="21"/>
+      <c r="Q127" s="21"/>
+    </row>
+    <row r="128" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B128" s="24"/>
+      <c r="C128" s="25"/>
+      <c r="D128" s="25"/>
+      <c r="E128" s="46"/>
+      <c r="F128" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G128" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H128" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I128" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="J128" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="K128" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="L128" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="M128" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="N128" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="O128" s="21"/>
+      <c r="P128" s="21"/>
+      <c r="Q128" s="21"/>
+    </row>
+    <row r="129" spans="2:17">
+      <c r="B129" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D129" s="30">
+        <v>9</v>
+      </c>
+      <c r="E129" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F129" s="32">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="G129" s="33">
+        <v>-0.05</v>
+      </c>
+      <c r="H129" s="33"/>
+      <c r="I129" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="J129" s="33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K129" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="L129" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="M129" s="33">
+        <v>0.16</v>
+      </c>
+      <c r="N129" s="34"/>
+      <c r="O129" s="21"/>
+      <c r="P129" s="21"/>
+      <c r="Q129" s="21"/>
+    </row>
+    <row r="130" spans="2:17">
+      <c r="B130" s="35"/>
+      <c r="C130" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D130" s="6">
+        <v>4</v>
+      </c>
+      <c r="E130" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F130" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="G130" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="H130" s="5"/>
+      <c r="I130" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J130" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="L130" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="M130" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="N130" s="8"/>
+      <c r="O130" s="21"/>
+      <c r="P130" s="21"/>
+      <c r="Q130" s="21"/>
+    </row>
+    <row r="131" spans="2:17">
+      <c r="B131" s="35"/>
+      <c r="C131" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D131" s="6">
+        <v>20</v>
+      </c>
+      <c r="E131" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F131" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="G131" s="5">
+        <v>-0.03</v>
+      </c>
+      <c r="H131" s="5"/>
+      <c r="I131" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="J131" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="L131" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="M131" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="N131" s="8"/>
+      <c r="O131" s="21"/>
+      <c r="P131" s="21"/>
+      <c r="Q131" s="21"/>
+    </row>
+    <row r="132" spans="2:17">
+      <c r="B132" s="35"/>
+      <c r="C132" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D132" s="6">
+        <v>26</v>
+      </c>
+      <c r="E132" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F132" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="G132" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="H132" s="5"/>
+      <c r="I132" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="J132" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="L132" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="M132" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="N132" s="8"/>
+      <c r="O132" s="21"/>
+      <c r="P132" s="21"/>
+      <c r="Q132" s="21"/>
+    </row>
+    <row r="133" spans="2:17">
+      <c r="B133" s="35"/>
+      <c r="C133" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D133" s="6">
+        <v>7</v>
+      </c>
+      <c r="E133" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F133" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="G133" s="5">
+        <v>-0.03</v>
+      </c>
+      <c r="H133" s="5"/>
+      <c r="I133" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="J133" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="L133" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="M133" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="N133" s="8"/>
+      <c r="O133" s="21"/>
+      <c r="P133" s="21"/>
+      <c r="Q133" s="21"/>
+    </row>
+    <row r="134" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B134" s="37"/>
+      <c r="C134" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D134" s="38"/>
+      <c r="E134" s="39"/>
+      <c r="F134" s="77">
+        <f>AVERAGE(F129:F133)</f>
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="G134" s="10">
+        <f>AVERAGE(G129:G133)</f>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="H134" s="10" t="e">
+        <f>AVERAGE(H129:H133)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I134" s="77">
+        <f>AVERAGE(I129:I133)</f>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="J134" s="10">
+        <f>AVERAGE(J129:J133)</f>
+        <v>0.21800000000000003</v>
+      </c>
+      <c r="K134" s="10">
+        <f>AVERAGE(K129:K133)</f>
+        <v>0.23200000000000004</v>
+      </c>
+      <c r="L134" s="9">
+        <f>AVERAGE(L129:L133)</f>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="M134" s="41">
+        <f>AVERAGE(M129:M133)</f>
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="N134" s="11" t="e">
+        <f>AVERAGE(N129:N133)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O134" s="21"/>
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+    </row>
+    <row r="135" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B135" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C135" s="21"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="44"/>
+      <c r="F135" s="21"/>
+      <c r="G135" s="21"/>
+      <c r="H135" s="21"/>
+      <c r="I135" s="21"/>
+      <c r="J135" s="21"/>
+      <c r="K135" s="21"/>
+      <c r="L135" s="21"/>
+      <c r="M135" s="21"/>
+      <c r="N135" s="21"/>
+      <c r="O135" s="21"/>
+      <c r="P135" s="21"/>
+      <c r="Q135" s="21"/>
+    </row>
+    <row r="136" spans="2:17">
+      <c r="B136" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C136" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D136" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E136" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G136" s="15"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J136" s="15"/>
+      <c r="K136" s="15"/>
+      <c r="L136" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="M136" s="15"/>
+      <c r="N136" s="16"/>
+    </row>
+    <row r="137" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B137" s="24"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="46"/>
+      <c r="F137" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G137" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H137" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I137" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="J137" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="K137" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="L137" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="M137" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="N137" s="52" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
+      <c r="B138" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C138" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D138" s="30">
+        <v>9</v>
+      </c>
+      <c r="E138" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F138" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="G138" s="33">
+        <v>0</v>
+      </c>
+      <c r="H138" s="33">
+        <v>-0.04</v>
+      </c>
+      <c r="I138" s="32">
+        <v>0.13</v>
+      </c>
+      <c r="J138" s="33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K138" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="L138" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="M138" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="N138" s="34">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17">
+      <c r="B139" s="35"/>
+      <c r="C139" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D139" s="6">
+        <v>4</v>
+      </c>
+      <c r="E139" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F139" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="G139" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="H139" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="I139" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="J139" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="L139" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="M139" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="N139" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17">
+      <c r="B140" s="35"/>
+      <c r="C140" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D140" s="6">
+        <v>20</v>
+      </c>
+      <c r="E140" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F140" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G140" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="H140" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="I140" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="J140" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="L140" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="M140" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="N140" s="8">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17">
+      <c r="B141" s="35"/>
+      <c r="C141" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D141" s="6">
+        <v>26</v>
+      </c>
+      <c r="E141" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F141" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="G141" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="H141" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="I141" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="J141" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="L141" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="M141" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="N141" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17">
+      <c r="B142" s="35"/>
+      <c r="C142" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D142" s="6">
+        <v>7</v>
+      </c>
+      <c r="E142" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F142" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G142" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H142" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I142" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="J142" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="L142" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M142" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="N142" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B143" s="37"/>
+      <c r="C143" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D143" s="38"/>
+      <c r="E143" s="39"/>
+      <c r="F143" s="77">
+        <f>AVERAGE(F138:F142)</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="G143" s="10">
+        <f>AVERAGE(G138:G142)</f>
+        <v>0.2</v>
+      </c>
+      <c r="H143" s="10">
+        <f>AVERAGE(H138:H142)</f>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="I143" s="77">
+        <f>AVERAGE(I138:I142)</f>
+        <v>0.25999999999999995</v>
+      </c>
+      <c r="J143" s="10">
+        <f>AVERAGE(J138:J142)</f>
+        <v>0.23800000000000004</v>
+      </c>
+      <c r="K143" s="10">
+        <f>AVERAGE(K138:K142)</f>
+        <v>0.23200000000000004</v>
+      </c>
+      <c r="L143" s="9">
+        <f>AVERAGE(L138:L142)</f>
+        <v>0.33799999999999997</v>
+      </c>
+      <c r="M143" s="41">
+        <f>AVERAGE(M138:M142)</f>
+        <v>0.378</v>
+      </c>
+      <c r="N143" s="11">
+        <f>AVERAGE(N138:N142)</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" ht="17.25" thickBot="1"/>
+    <row r="145" spans="2:17">
+      <c r="B145" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" s="67"/>
+      <c r="D145" s="67"/>
+      <c r="E145" s="68"/>
+      <c r="F145" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="G145" s="67"/>
+      <c r="H145" s="67"/>
+      <c r="I145" s="67"/>
+      <c r="J145" s="68"/>
+      <c r="K145" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="L145" s="67"/>
+      <c r="M145" s="67"/>
+      <c r="N145" s="68"/>
+      <c r="O145" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="P145" s="67"/>
+      <c r="Q145" s="68"/>
+    </row>
+    <row r="146" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B146" s="69"/>
+      <c r="C146" s="70"/>
+      <c r="D146" s="70"/>
+      <c r="E146" s="75"/>
+      <c r="F146" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="G146" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="H146" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="I146" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="J146" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="K146" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="L146" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="M146" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="N146" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="O146" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="P146" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q146" s="72" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17">
+      <c r="B147" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C147" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="D147" s="61">
+        <v>9</v>
+      </c>
+      <c r="E147" s="62">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F147" s="63">
+        <v>-2.29289593740678E-2</v>
+      </c>
+      <c r="G147" s="64">
+        <v>0.11104297240348029</v>
+      </c>
+      <c r="H147" s="65">
+        <v>0.20816679944749111</v>
+      </c>
+      <c r="I147" s="64">
+        <v>0.14620539933031881</v>
+      </c>
+      <c r="J147" s="64">
+        <v>0.1081797667134011</v>
+      </c>
+      <c r="K147" s="63">
+        <v>-1.37293528683901E-2</v>
+      </c>
+      <c r="L147" s="64">
+        <v>-0.10540960290521301</v>
+      </c>
+      <c r="M147" s="64">
+        <v>-0.04</v>
+      </c>
+      <c r="N147" s="64">
+        <v>4.3814197611345897E-2</v>
+      </c>
+      <c r="O147" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="P147" s="64">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="33">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17">
+      <c r="B148" s="35"/>
+      <c r="C148" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D148" s="6">
+        <v>4</v>
+      </c>
+      <c r="E148" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F148" s="7">
+        <v>0.37489881673411651</v>
+      </c>
+      <c r="G148" s="5">
+        <v>0.25499828429792482</v>
+      </c>
+      <c r="H148" s="5">
+        <v>0.26534498448963351</v>
+      </c>
+      <c r="I148" s="5">
+        <v>0.26365068206527531</v>
+      </c>
+      <c r="J148" s="5">
+        <v>0.114596640197212</v>
+      </c>
+      <c r="K148" s="7">
+        <v>0.2449390044497595</v>
+      </c>
+      <c r="L148" s="5">
+        <v>0.31782197948522511</v>
+      </c>
+      <c r="M148" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="N148" s="57">
+        <v>0.38010350927102837</v>
+      </c>
+      <c r="O148" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="P148" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="Q148" s="5">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17">
+      <c r="B149" s="35"/>
+      <c r="C149" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D149" s="6">
+        <v>20</v>
+      </c>
+      <c r="E149" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F149" s="7">
+        <v>0.12874780747418349</v>
+      </c>
+      <c r="G149" s="5">
+        <v>0.1002839418749927</v>
+      </c>
+      <c r="H149" s="57">
+        <v>0.59983910377182004</v>
+      </c>
+      <c r="I149" s="5">
+        <v>0.23352612172222539</v>
+      </c>
+      <c r="J149" s="5">
+        <v>0.15956732284347261</v>
+      </c>
+      <c r="K149" s="7">
+        <v>9.4263370089226806E-2</v>
+      </c>
+      <c r="L149" s="5">
+        <v>0.15957805213997139</v>
+      </c>
+      <c r="M149" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="N149" s="5">
+        <v>6.4579444589532103E-2</v>
+      </c>
+      <c r="O149" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="P149" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="Q149" s="5">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17">
+      <c r="B150" s="35"/>
+      <c r="C150" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D150" s="6">
+        <v>26</v>
+      </c>
+      <c r="E150" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F150" s="58">
+        <v>0.65994752501984588</v>
+      </c>
+      <c r="G150" s="5">
+        <v>0.56752175328716459</v>
+      </c>
+      <c r="H150" s="5">
+        <v>0.57332092640077525</v>
+      </c>
+      <c r="I150" s="5">
+        <v>0.54287250276626031</v>
+      </c>
+      <c r="J150" s="5">
+        <v>0.47163897670942651</v>
+      </c>
+      <c r="K150" s="7">
+        <v>0.36399765051157551</v>
+      </c>
+      <c r="L150" s="5">
+        <v>0.62256923945283416</v>
+      </c>
+      <c r="M150" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="N150" s="5">
+        <v>0.53654385012449213</v>
+      </c>
+      <c r="O150" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="P150" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="Q150" s="5">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17">
+      <c r="B151" s="35"/>
+      <c r="C151" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D151" s="6">
+        <v>7</v>
+      </c>
+      <c r="E151" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F151" s="12">
+        <v>2.8856522129765E-3</v>
+      </c>
+      <c r="G151" s="5">
+        <v>0.1424025927312777</v>
+      </c>
+      <c r="H151" s="5">
+        <v>1.7039340308251001E-2</v>
+      </c>
+      <c r="I151" s="57">
+        <v>0.31921754446642447</v>
+      </c>
+      <c r="J151" s="5">
+        <v>0.32018091023970308</v>
+      </c>
+      <c r="K151" s="7">
+        <v>9.0873256876832897E-2</v>
+      </c>
+      <c r="L151" s="5">
+        <v>-7.2669713659328002E-3</v>
+      </c>
+      <c r="M151" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N151" s="5">
+        <v>0.1133115677139481</v>
+      </c>
+      <c r="O151" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="P151" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q151" s="5">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B152" s="37"/>
+      <c r="C152" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D152" s="38"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="40">
+        <v>0.22871016841341091</v>
+      </c>
+      <c r="G152" s="10">
+        <v>0.23524990891896799</v>
+      </c>
+      <c r="H152" s="41">
+        <v>0.33274223088359417</v>
+      </c>
+      <c r="I152" s="10">
+        <v>0.30109445007010088</v>
+      </c>
+      <c r="J152" s="10">
+        <v>0.23483272334064303</v>
+      </c>
+      <c r="K152" s="9">
+        <v>0.15606878581180092</v>
+      </c>
+      <c r="L152" s="10">
+        <v>0.19745853936137697</v>
+      </c>
+      <c r="M152" s="10">
+        <f>AVERAGE(M147:M151)</f>
+        <v>0.184</v>
+      </c>
+      <c r="N152" s="41">
+        <v>0.2276705138620693</v>
+      </c>
+      <c r="O152" s="9">
+        <f>AVERAGE(O147:O151)</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="P152" s="10">
+        <f>AVERAGE(P147:P151)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q152" s="10">
+        <f>AVERAGE(Q147:Q151)</f>
+        <v>0.17399999999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17">
+      <c r="B153" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C153" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D153" s="30">
+        <v>9</v>
+      </c>
+      <c r="E153" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F153" s="32">
+        <v>0.15419838781907741</v>
+      </c>
+      <c r="G153" s="33">
+        <v>0.2569763569763569</v>
+      </c>
+      <c r="H153" s="56">
+        <v>0.26619362327183083</v>
+      </c>
+      <c r="I153" s="33">
+        <v>0.23560755197787669</v>
+      </c>
+      <c r="J153" s="34">
+        <v>0.2336836588326161</v>
+      </c>
+      <c r="K153" s="32">
+        <v>0.14440376793317969</v>
+      </c>
+      <c r="L153" s="33">
+        <v>0.19935844788384069</v>
+      </c>
+      <c r="M153" s="33">
+        <v>0.18</v>
+      </c>
+      <c r="N153" s="34">
+        <v>0.22231585460925779</v>
+      </c>
+      <c r="O153" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="P153" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="Q153" s="34">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17">
+      <c r="B154" s="35"/>
+      <c r="C154" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D154" s="6">
+        <v>4</v>
+      </c>
+      <c r="E154" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F154" s="7">
+        <v>0.51875783131231035</v>
+      </c>
+      <c r="G154" s="5">
+        <v>0.41333698707799421</v>
+      </c>
+      <c r="H154" s="5">
+        <v>0.42605596975478549</v>
+      </c>
+      <c r="I154" s="5">
+        <v>0.29370168482053122</v>
+      </c>
+      <c r="J154" s="8">
+        <v>0.25246203532908379</v>
+      </c>
+      <c r="K154" s="7">
+        <v>0.5081655420242116</v>
+      </c>
+      <c r="L154" s="5">
+        <v>0.57748118796846803</v>
+      </c>
+      <c r="M154" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="N154" s="59">
+        <v>0.60832340439586807</v>
+      </c>
+      <c r="O154" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="P154" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="Q154" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17">
+      <c r="B155" s="35"/>
+      <c r="C155" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D155" s="6">
+        <v>20</v>
+      </c>
+      <c r="E155" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F155" s="7">
+        <v>0.19913208925900139</v>
+      </c>
+      <c r="G155" s="5">
+        <v>0.18389577305456389</v>
+      </c>
+      <c r="H155" s="57">
+        <v>0.6292013818329607</v>
+      </c>
+      <c r="I155" s="5">
+        <v>0.23388541198367141</v>
+      </c>
+      <c r="J155" s="8">
+        <v>0.2229615657973866</v>
+      </c>
+      <c r="K155" s="7">
+        <v>0.16534391534391529</v>
+      </c>
+      <c r="L155" s="5">
+        <v>0.22257601835915089</v>
+      </c>
+      <c r="M155" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="N155" s="8">
+        <v>0.15548472413485029</v>
+      </c>
+      <c r="O155" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="P155" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="Q155" s="8">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17">
+      <c r="B156" s="35"/>
+      <c r="C156" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D156" s="6">
+        <v>26</v>
+      </c>
+      <c r="E156" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F156" s="58">
+        <v>0.82981745842702936</v>
+      </c>
+      <c r="G156" s="5">
+        <v>0.7225678177371978</v>
+      </c>
+      <c r="H156" s="5">
+        <v>0.7635614679783036</v>
+      </c>
+      <c r="I156" s="5">
+        <v>0.75422242134607731</v>
+      </c>
+      <c r="J156" s="8">
+        <v>0.66673056374009465</v>
+      </c>
+      <c r="K156" s="7">
+        <v>0.58761899478372315</v>
+      </c>
+      <c r="L156" s="5">
+        <v>0.81184607968002642</v>
+      </c>
+      <c r="M156" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="N156" s="8">
+        <v>0.73829246091240097</v>
+      </c>
+      <c r="O156" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="P156" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="Q156" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17">
+      <c r="B157" s="35"/>
+      <c r="C157" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D157" s="6">
+        <v>7</v>
+      </c>
+      <c r="E157" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F157" s="7">
+        <v>0.14540283706075019</v>
+      </c>
+      <c r="G157" s="5">
+        <v>0.2845092449922958</v>
+      </c>
+      <c r="H157" s="5">
+        <v>0.18273850672353251</v>
+      </c>
+      <c r="I157" s="5">
+        <v>0.3089673913043478</v>
+      </c>
+      <c r="J157" s="59">
+        <v>0.31583268516117879</v>
+      </c>
+      <c r="K157" s="7">
+        <v>0.2145976949103475</v>
+      </c>
+      <c r="L157" s="5">
+        <v>0.18591184806389291</v>
+      </c>
+      <c r="M157" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="N157" s="8">
+        <v>0.2437281908051368</v>
+      </c>
+      <c r="O157" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P157" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B158" s="37"/>
+      <c r="C158" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D158" s="38"/>
+      <c r="E158" s="39"/>
+      <c r="F158" s="9">
+        <v>0.36946172077563377</v>
+      </c>
+      <c r="G158" s="10">
+        <v>0.37225723596768168</v>
+      </c>
+      <c r="H158" s="41">
+        <v>0.45355018991228269</v>
+      </c>
+      <c r="I158" s="10">
+        <v>0.3652768922865009</v>
+      </c>
+      <c r="J158" s="11">
+        <v>0.33833410177207196</v>
+      </c>
+      <c r="K158" s="9">
+        <v>0.32402598299907542</v>
+      </c>
+      <c r="L158" s="41">
+        <v>0.39943471639107575</v>
+      </c>
+      <c r="M158" s="10">
+        <f>AVERAGE(M153:M157)</f>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="N158" s="11">
+        <v>0.39362892697150281</v>
+      </c>
+      <c r="O158" s="9">
+        <f>AVERAGE(O153:O157)</f>
+        <v>0.33799999999999997</v>
+      </c>
+      <c r="P158" s="10">
+        <f>AVERAGE(P153:P157)</f>
+        <v>0.378</v>
+      </c>
+      <c r="Q158" s="11">
+        <f>AVERAGE(Q153:Q157)</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17">
+      <c r="B159" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C159" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D159" s="30">
+        <v>9</v>
+      </c>
+      <c r="E159" s="31">
+        <v>6.5217391304347797E-2</v>
+      </c>
+      <c r="F159" s="32">
+        <v>8.0466328844669199E-2</v>
+      </c>
+      <c r="G159" s="33">
+        <v>0.22388642099032249</v>
+      </c>
+      <c r="H159" s="33">
+        <v>0.28386696660446481</v>
+      </c>
+      <c r="I159" s="56">
+        <v>0.2903137891903988</v>
+      </c>
+      <c r="J159" s="33">
+        <v>0.1349380025519544</v>
+      </c>
+      <c r="K159" s="32">
+        <v>0.106206508276523</v>
+      </c>
+      <c r="L159" s="33">
+        <v>5.3302310692446203E-2</v>
+      </c>
+      <c r="M159" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="N159" s="33">
+        <v>8.8111977440462105E-2</v>
+      </c>
+      <c r="O159" s="32">
+        <v>0.13</v>
+      </c>
+      <c r="P159" s="33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q159" s="33">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17">
+      <c r="B160" s="35"/>
+      <c r="C160" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D160" s="6">
+        <v>4</v>
+      </c>
+      <c r="E160" s="36">
+        <v>2.8985507246376802E-2</v>
+      </c>
+      <c r="F160" s="58">
+        <v>0.4428281980325674</v>
+      </c>
+      <c r="G160" s="5">
+        <v>0.33047091048446359</v>
+      </c>
+      <c r="H160" s="5">
+        <v>0.28956775940810248</v>
+      </c>
+      <c r="I160" s="5">
+        <v>0.3661273080317069</v>
+      </c>
+      <c r="J160" s="5">
+        <v>0.24454188308182781</v>
+      </c>
+      <c r="K160" s="7">
+        <v>0.27588990364014421</v>
+      </c>
+      <c r="L160" s="5">
+        <v>0.32762517404119601</v>
+      </c>
+      <c r="M160" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="N160" s="5">
+        <v>0.36051157011691348</v>
+      </c>
+      <c r="O160" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="P160" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q160" s="5">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17">
+      <c r="B161" s="35"/>
+      <c r="C161" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D161" s="6">
+        <v>20</v>
+      </c>
+      <c r="E161" s="36">
+        <v>0.14492753623188401</v>
+      </c>
+      <c r="F161" s="7">
+        <v>0.11283035173745939</v>
+      </c>
+      <c r="G161" s="5">
+        <v>0.1176701275613196</v>
+      </c>
+      <c r="H161" s="57">
+        <v>0.53659149370519876</v>
+      </c>
+      <c r="I161" s="5">
+        <v>0.32220542968429322</v>
+      </c>
+      <c r="J161" s="5">
+        <v>0.25000162650352181</v>
+      </c>
+      <c r="K161" s="7">
+        <v>0.1332734549267339</v>
+      </c>
+      <c r="L161" s="5">
+        <v>6.00433424523956E-2</v>
+      </c>
+      <c r="M161" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="N161" s="5">
+        <v>5.3488880143233601E-2</v>
+      </c>
+      <c r="O161" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="P161" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="Q161" s="5">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17">
+      <c r="B162" s="35"/>
+      <c r="C162" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D162" s="6">
+        <v>26</v>
+      </c>
+      <c r="E162" s="36">
+        <v>0.1884057971014492</v>
+      </c>
+      <c r="F162" s="7">
+        <v>0.58843231868482548</v>
+      </c>
+      <c r="G162" s="57">
+        <v>0.71171151379063791</v>
+      </c>
+      <c r="H162" s="5">
+        <v>0.63834223610673113</v>
+      </c>
+      <c r="I162" s="5">
+        <v>0.53750188071166249</v>
+      </c>
+      <c r="J162" s="5">
+        <v>0.47247469691121918</v>
+      </c>
+      <c r="K162" s="7">
+        <v>0.43211204083057497</v>
+      </c>
+      <c r="L162" s="5">
+        <v>0.56640214195500771</v>
+      </c>
+      <c r="M162" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N162" s="5">
+        <v>0.5649804413614824</v>
+      </c>
+      <c r="O162" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="P162" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="Q162" s="5">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17">
+      <c r="B163" s="35"/>
+      <c r="C163" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" s="6">
+        <v>7</v>
+      </c>
+      <c r="E163" s="36">
+        <v>5.0724637681159403E-2</v>
+      </c>
+      <c r="F163" s="7">
+        <v>5.8338376712800698E-2</v>
+      </c>
+      <c r="G163" s="5">
+        <v>0.1007110699960103</v>
+      </c>
+      <c r="H163" s="5">
+        <v>9.5524986816998003E-2</v>
+      </c>
+      <c r="I163" s="57">
+        <v>0.39878437563383168</v>
+      </c>
+      <c r="J163" s="5">
+        <v>0.41246008383159438</v>
+      </c>
+      <c r="K163" s="7">
+        <v>0.14391609274123679</v>
+      </c>
+      <c r="L163" s="5">
+        <v>5.66250373030069E-2</v>
+      </c>
+      <c r="M163" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="N163" s="5">
+        <v>0.1508813651521474</v>
+      </c>
+      <c r="O163" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="P163" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="Q163" s="5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17" ht="17.25" thickBot="1">
+      <c r="B164" s="37"/>
+      <c r="C164" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D164" s="38"/>
+      <c r="E164" s="39"/>
+      <c r="F164" s="40">
+        <v>0.25657911480246443</v>
+      </c>
+      <c r="G164" s="42">
+        <v>0.29689000856455078</v>
+      </c>
+      <c r="H164" s="42">
+        <v>0.36877868852829909</v>
+      </c>
+      <c r="I164" s="43">
+        <v>0.38298655665037862</v>
+      </c>
+      <c r="J164" s="42">
+        <v>0.30288325857602355</v>
+      </c>
+      <c r="K164" s="9">
+        <v>0.21827960008304256</v>
+      </c>
+      <c r="L164" s="10">
+        <v>0.21279960128881048</v>
+      </c>
+      <c r="M164" s="41">
+        <f>AVERAGE(M159:M163)</f>
+        <v>0.24200000000000005</v>
+      </c>
+      <c r="N164" s="41">
+        <v>0.2435948468428478</v>
+      </c>
+      <c r="O164" s="9">
+        <f>AVERAGE(O159:O163)</f>
+        <v>0.25999999999999995</v>
+      </c>
+      <c r="P164" s="10">
+        <f>AVERAGE(P159:P163)</f>
+        <v>0.23800000000000004</v>
+      </c>
+      <c r="Q164" s="10">
+        <f>AVERAGE(Q159:Q163)</f>
+        <v>0.23200000000000004</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="B99:B104"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="J85:M85"/>
-    <mergeCell ref="N85:Q85"/>
+  <mergeCells count="53">
     <mergeCell ref="D85:D86"/>
     <mergeCell ref="E85:E86"/>
-    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="L85:N85"/>
+    <mergeCell ref="B159:B164"/>
+    <mergeCell ref="B145:E146"/>
+    <mergeCell ref="F145:J145"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="E127:E128"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="I127:K127"/>
+    <mergeCell ref="B129:B134"/>
+    <mergeCell ref="B147:B152"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="I136:K136"/>
+    <mergeCell ref="L136:N136"/>
+    <mergeCell ref="B153:B158"/>
+    <mergeCell ref="K145:N145"/>
+    <mergeCell ref="O145:Q145"/>
+    <mergeCell ref="L127:N127"/>
+    <mergeCell ref="B138:B143"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="B114:B119"/>
+    <mergeCell ref="B120:B125"/>
+    <mergeCell ref="F106:I106"/>
+    <mergeCell ref="J106:M106"/>
+    <mergeCell ref="N106:Q106"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="B108:B113"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="B72:B77"/>
     <mergeCell ref="B78:B83"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
     <mergeCell ref="B85:B86"/>
     <mergeCell ref="C85:C86"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="B99:B104"/>
     <mergeCell ref="B66:B71"/>
     <mergeCell ref="D64:D65"/>
     <mergeCell ref="E64:E65"/>
@@ -4631,14 +7418,99 @@
     <mergeCell ref="P64:T64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J87:M103">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND($E87&lt;&gt;"",J87&lt;$E87)</formula>
+  <conditionalFormatting sqref="J108:M124 I138:K142">
+    <cfRule type="expression" dxfId="20" priority="24">
+      <formula>AND($E108&lt;&gt;"",I108&lt;$E108)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66:O82">
+    <cfRule type="expression" dxfId="19" priority="22">
+      <formula>AND($E66&lt;&gt;"",K66&lt;$E66)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H113">
+    <cfRule type="expression" dxfId="18" priority="21">
+      <formula>AND($E113&lt;&gt;"",H113&lt;$E113)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F159:J163">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>AND($E159&lt;&gt;"",F159&lt;$E159)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K159:N163">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>AND($E159&lt;&gt;"",K159&lt;$E159)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O159:P163">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>AND($E159&lt;&gt;"",O159&lt;$E159)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J87:K91 I92:K98 I99:J103">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>AND($E87&lt;&gt;"",I87&lt;$E87)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H92">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>AND($E92&lt;&gt;"",H92&lt;$E92)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G92">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>AND($E92&lt;&gt;"",G92&lt;$E92)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H98">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>AND($E98&lt;&gt;"",H98&lt;$E98)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G98">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>AND($E98&lt;&gt;"",G98&lt;$E98)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q159:Q163">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>AND($E159&lt;&gt;"",Q159&lt;$E159)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I104:J104">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>AND($E104&lt;&gt;"",I104&lt;$E104)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G104">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AND($E104&lt;&gt;"",G104&lt;$E104)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H125">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>AND($E125&lt;&gt;"",H125&lt;$E125)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L120:L124">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AND($E110&lt;&gt;"",L120&lt;$E110)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L125">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AND($E115&lt;&gt;"",L125&lt;$E115)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K99:K103">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($E99&lt;&gt;"",K99&lt;$E99)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I129:K133">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($E66&lt;&gt;"",K66&lt;$E66)</formula>
+      <formula>AND($E129&lt;&gt;"",I129&lt;$E129)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
